--- a/Assets/Data/Data.xlsx
+++ b/Assets/Data/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity Projects\army-roguelike\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BA1BB51-C9EA-4F09-8BEB-C3FC492A0897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CCC88436-5A2B-43EF-8D19-E8E78C623C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{9E458342-0A01-4C67-9C5A-29659238C628}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="32">
   <si>
     <t>Num Code</t>
   </si>
@@ -122,6 +122,24 @@
   </si>
   <si>
     <t>Sprite</t>
+  </si>
+  <si>
+    <t>Fast Melee</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>Basic Unit</t>
+  </si>
+  <si>
+    <t>Tanky Melee</t>
+  </si>
+  <si>
+    <t>Ranged</t>
   </si>
 </sst>
 </file>
@@ -629,7 +647,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{017D5791-C040-4950-98E5-C0B8B3A5B81B}" name="UnitList11" displayName="UnitList11" ref="A1:M24" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{017D5791-C040-4950-98E5-C0B8B3A5B81B}" name="UnitIdeasList" displayName="UnitIdeasList" ref="A1:M24" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10">
   <autoFilter ref="A1:M24" xr:uid="{6DC2E09C-A7AA-4D9F-AEC7-68E9417564A3}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{625AB9E1-16DE-4EC0-B800-4D11257701ED}" name="Num Code" dataDxfId="8"/>
@@ -651,7 +669,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{11F1B7EC-5D3B-4EA2-AE84-93D707E55561}" name="StructureList10" displayName="StructureList10" ref="A1:L32" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{11F1B7EC-5D3B-4EA2-AE84-93D707E55561}" name="StructureIdeasList" displayName="StructureIdeasList" ref="A1:L32" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14">
   <autoFilter ref="A1:L32" xr:uid="{400789E9-1FDC-425D-B469-26BDDE1A39C5}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{6D981389-587D-4719-B887-0DBBA673ACE7}" name="Num Code" dataDxfId="12"/>
@@ -1082,135 +1100,373 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
       <c r="C2" s="9"/>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1">
+        <v>50</v>
+      </c>
+      <c r="I2" s="1">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="L2" s="1">
+        <v>2</v>
+      </c>
+      <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
       <c r="C3" s="9"/>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1">
+        <v>20</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="L3" s="1">
+        <v>4</v>
+      </c>
+      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
       <c r="C4" s="9"/>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="1">
+        <v>5</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
       <c r="C5" s="9"/>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>40</v>
+      </c>
+      <c r="I5" s="1">
+        <v>10</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1">
+        <v>10</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="9"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="C7" s="9"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="C8" s="9"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="C9" s="9"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="C10" s="9"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="C11" s="9"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="C12" s="9"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="C13" s="9"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="C14" s="9"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="C15" s="9"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="C16" s="9"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="C17" s="9"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="C18" s="9"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="C19" s="9"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="C20" s="9"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="C21" s="9"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="C22" s="9"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="C23" s="9"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1292,6 +1548,12 @@
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2005,6 +2267,9 @@
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
       <c r="G4" t="s">
         <v>21</v>
       </c>

--- a/Assets/Data/Data.xlsx
+++ b/Assets/Data/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity Projects\army-roguelike\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CCC88436-5A2B-43EF-8D19-E8E78C623C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A17C5E7-F0DC-493C-A72B-EA87774011AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{9E458342-0A01-4C67-9C5A-29659238C628}"/>
+    <workbookView xWindow="20250" yWindow="21555" windowWidth="29040" windowHeight="16440" xr2:uid="{9E458342-0A01-4C67-9C5A-29659238C628}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="29">
   <si>
     <t>Num Code</t>
   </si>
@@ -124,22 +124,13 @@
     <t>Sprite</t>
   </si>
   <si>
-    <t>Fast Melee</t>
-  </si>
-  <si>
     <t>Test</t>
   </si>
   <si>
     <t>Basic</t>
   </si>
   <si>
-    <t>Basic Unit</t>
-  </si>
-  <si>
-    <t>Tanky Melee</t>
-  </si>
-  <si>
-    <t>Ranged</t>
+    <t>Attack Dmg</t>
   </si>
 </sst>
 </file>
@@ -307,9 +298,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -319,6 +307,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -327,6 +318,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -349,20 +354,6 @@
       <fill>
         <patternFill>
           <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -385,23 +376,56 @@
       </font>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FF284E3F"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="medium">
           <color rgb="FF284E3F"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color rgb="FF284E3F"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -429,20 +453,23 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FF284E3F"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="medium">
           <color rgb="FF284E3F"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color rgb="FF284E3F"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -470,7 +497,21 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FF284E3F"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF284E3F"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -497,7 +538,17 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FF284E3F"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <border outline="0">
@@ -505,31 +556,6 @@
           <color rgb="FF284E3F"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color rgb="FF284E3F"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -555,41 +581,6 @@
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF284E3F"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color rgb="FF284E3F"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -604,18 +595,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6DC2E09C-A7AA-4D9F-AEC7-68E9417564A3}" name="UnitList" displayName="UnitList" ref="A1:M24" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="19" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6DC2E09C-A7AA-4D9F-AEC7-68E9417564A3}" name="UnitList" displayName="UnitList" ref="A1:M24" totalsRowShown="0" headerRowDxfId="26" headerRowBorderDxfId="25" tableBorderDxfId="24">
   <autoFilter ref="A1:M24" xr:uid="{6DC2E09C-A7AA-4D9F-AEC7-68E9417564A3}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{2610CF47-B356-4971-AAAF-960A2A01718D}" name="Num Code" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{2610CF47-B356-4971-AAAF-960A2A01718D}" name="Num Code" dataDxfId="23"/>
     <tableColumn id="2" xr3:uid="{B33CD085-9449-44D8-8623-EF20F4A730BE}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{BD534C9A-0DC1-44B0-9782-C17FE125AB13}" name="Description" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{BD534C9A-0DC1-44B0-9782-C17FE125AB13}" name="Description" dataDxfId="22"/>
     <tableColumn id="4" xr3:uid="{03BB7CDF-7FD0-4E87-9FEA-5F2F433508A4}" name="Notes"/>
     <tableColumn id="5" xr3:uid="{C33A625E-B77F-47E2-989A-674A0B368D83}" name="Archetype"/>
     <tableColumn id="6" xr3:uid="{CC3CFC1C-661A-41B1-86CC-CDD82F71F11A}" name="Structure"/>
     <tableColumn id="7" xr3:uid="{7B28ED4F-F996-49AE-99B0-A84E09416ECE}" name="Size"/>
     <tableColumn id="8" xr3:uid="{AA11BEE3-DBFF-4FAC-B921-D630556ECF81}" name="Health"/>
-    <tableColumn id="9" xr3:uid="{BC53EB70-D146-420F-8024-020D366CA491}" name="Attack"/>
+    <tableColumn id="9" xr3:uid="{BC53EB70-D146-420F-8024-020D366CA491}" name="Attack Dmg"/>
     <tableColumn id="10" xr3:uid="{094E56FD-4C38-4483-B078-60B1D2777FED}" name="Attack Speed"/>
     <tableColumn id="11" xr3:uid="{CB8588EB-4111-47C0-BC1F-F3330156DB7F}" name="Attack Range"/>
     <tableColumn id="12" xr3:uid="{1C0EB30A-5A92-4218-B0D6-CE9DCB496B22}" name="Move Speed"/>
@@ -626,10 +617,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{400789E9-1FDC-425D-B469-26BDDE1A39C5}" name="StructureList" displayName="StructureList" ref="A1:L32" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="24" tableBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{400789E9-1FDC-425D-B469-26BDDE1A39C5}" name="StructureList" displayName="StructureList" ref="A1:L32" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19">
   <autoFilter ref="A1:L32" xr:uid="{400789E9-1FDC-425D-B469-26BDDE1A39C5}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{4F161D77-D32E-4CC8-BDAD-57272CBABBA1}" name="Num Code" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{4F161D77-D32E-4CC8-BDAD-57272CBABBA1}" name="Num Code" dataDxfId="18"/>
     <tableColumn id="2" xr3:uid="{E6D266AE-13C6-4E3C-B90B-4194E09792FB}" name="Name"/>
     <tableColumn id="3" xr3:uid="{36B9052A-7BD2-4E8E-8ED3-2436C7B1CD54}" name="Description"/>
     <tableColumn id="4" xr3:uid="{0DA27FB7-8528-4BAB-AA50-86CB7E1C9078}" name="Notes"/>
@@ -647,12 +638,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{017D5791-C040-4950-98E5-C0B8B3A5B81B}" name="UnitIdeasList" displayName="UnitIdeasList" ref="A1:M24" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{017D5791-C040-4950-98E5-C0B8B3A5B81B}" name="UnitIdeasList" displayName="UnitIdeasList" ref="A1:M24" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15">
   <autoFilter ref="A1:M24" xr:uid="{6DC2E09C-A7AA-4D9F-AEC7-68E9417564A3}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{625AB9E1-16DE-4EC0-B800-4D11257701ED}" name="Num Code" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{625AB9E1-16DE-4EC0-B800-4D11257701ED}" name="Num Code" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{705C7AA4-59C3-46CC-9089-224094203780}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{675CDC35-18EE-471F-A5B6-7C5C67978A77}" name="Description" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{675CDC35-18EE-471F-A5B6-7C5C67978A77}" name="Description" dataDxfId="13"/>
     <tableColumn id="4" xr3:uid="{276D14A3-D533-42F7-83CF-52C5AF3F0CEA}" name="Notes"/>
     <tableColumn id="5" xr3:uid="{6C9F7AFD-6E29-4C86-933D-D1918F9F85F1}" name="Archetype"/>
     <tableColumn id="6" xr3:uid="{881F20FB-BB1B-41E5-AA90-319F0CF121F0}" name="Structure"/>
@@ -669,10 +660,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{11F1B7EC-5D3B-4EA2-AE84-93D707E55561}" name="StructureIdeasList" displayName="StructureIdeasList" ref="A1:L32" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{11F1B7EC-5D3B-4EA2-AE84-93D707E55561}" name="StructureIdeasList" displayName="StructureIdeasList" ref="A1:L32" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="11" tableBorderDxfId="10">
   <autoFilter ref="A1:L32" xr:uid="{400789E9-1FDC-425D-B469-26BDDE1A39C5}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{6D981389-587D-4719-B887-0DBBA673ACE7}" name="Num Code" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{6D981389-587D-4719-B887-0DBBA673ACE7}" name="Num Code" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{C2E41A71-1BF7-410D-A582-806AD8002B1F}" name="Name"/>
     <tableColumn id="3" xr3:uid="{3671C45D-4A32-4868-A266-9211FE5E342C}" name="Description"/>
     <tableColumn id="4" xr3:uid="{C7FE47C4-43CC-43DE-B06F-4C661D8FC825}" name="Notes"/>
@@ -690,7 +681,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4D0C8FBB-8770-4E9F-93B2-8B7F20071564}" name="ResourceList" displayName="ResourceList" ref="A1:B6" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4D0C8FBB-8770-4E9F-93B2-8B7F20071564}" name="ResourceList" displayName="ResourceList" ref="A1:B6" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A1:B6" xr:uid="{4D0C8FBB-8770-4E9F-93B2-8B7F20071564}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{1A510BD5-1379-4475-8891-02463B7EB7AE}" name="Name"/>
@@ -701,7 +692,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1050738E-B943-4A91-AB2B-A46FF21E14EA}" name="ArchetypeList" displayName="ArchetypeList" ref="B3:E10" totalsRowShown="0" headerRowDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1050738E-B943-4A91-AB2B-A46FF21E14EA}" name="ArchetypeList" displayName="ArchetypeList" ref="B3:E10" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="B3:E10" xr:uid="{1050738E-B943-4A91-AB2B-A46FF21E14EA}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{2B341702-4624-460A-B095-7A37F5B94F69}" name="Name"/>
@@ -714,7 +705,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B0212731-2C4C-471B-9DDF-C60945FE0920}" name="RarityList" displayName="RarityList" ref="G3:H6" totalsRowShown="0" headerRowDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B0212731-2C4C-471B-9DDF-C60945FE0920}" name="RarityList" displayName="RarityList" ref="G3:H6" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="G3:H6" xr:uid="{B0212731-2C4C-471B-9DDF-C60945FE0920}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{89EB797E-68EE-4F92-BDCE-C8DB39F9AE03}" name="Rarity"/>
@@ -1050,6 +1041,7 @@
     <col min="4" max="4" width="34.7109375" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
     <col min="10" max="11" width="14.140625" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
@@ -1081,7 +1073,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>9</v>
@@ -1089,10 +1081,10 @@
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1100,15 +1092,12 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="9"/>
+      <c r="C2" s="8"/>
       <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
         <v>27</v>
-      </c>
-      <c r="F2" t="s">
-        <v>28</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
@@ -1134,15 +1123,12 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="8"/>
+      <c r="E3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>27</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
@@ -1168,15 +1154,12 @@
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="9"/>
+      <c r="C4" s="8"/>
       <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
         <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
       </c>
       <c r="G4" s="1">
         <v>1</v>
@@ -1202,15 +1185,12 @@
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="9"/>
+      <c r="C5" s="8"/>
       <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
         <v>27</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1236,7 +1216,7 @@
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="C6" s="9"/>
+      <c r="C6" s="8"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -1249,7 +1229,7 @@
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="C7" s="9"/>
+      <c r="C7" s="8"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -1262,7 +1242,7 @@
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="C8" s="9"/>
+      <c r="C8" s="8"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -1275,7 +1255,7 @@
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="C9" s="9"/>
+      <c r="C9" s="8"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -1288,7 +1268,7 @@
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="C10" s="9"/>
+      <c r="C10" s="8"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1301,7 +1281,7 @@
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="C11" s="9"/>
+      <c r="C11" s="8"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1314,7 +1294,7 @@
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="C12" s="9"/>
+      <c r="C12" s="8"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1327,7 +1307,7 @@
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="C13" s="9"/>
+      <c r="C13" s="8"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1340,7 +1320,7 @@
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="C14" s="9"/>
+      <c r="C14" s="8"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -1353,7 +1333,7 @@
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="C15" s="9"/>
+      <c r="C15" s="8"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1366,7 +1346,7 @@
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="C16" s="9"/>
+      <c r="C16" s="8"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1379,7 +1359,7 @@
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="C17" s="9"/>
+      <c r="C17" s="8"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1392,7 +1372,7 @@
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="C18" s="9"/>
+      <c r="C18" s="8"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1405,7 +1385,7 @@
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="C19" s="9"/>
+      <c r="C19" s="8"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1418,7 +1398,7 @@
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="C20" s="9"/>
+      <c r="C20" s="8"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1431,7 +1411,7 @@
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="C21" s="9"/>
+      <c r="C21" s="8"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -1444,7 +1424,7 @@
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="C22" s="9"/>
+      <c r="C22" s="8"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1457,7 +1437,7 @@
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="8"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1470,7 +1450,7 @@
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="C24" s="9"/>
+      <c r="C24" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1541,7 +1521,7 @@
       <c r="K1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1550,10 +1530,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1707,17 +1687,17 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F2:F31">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>"Rare"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F32">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"Uncommon"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"Common"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F31">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"Rare"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -1789,10 +1769,10 @@
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1800,139 +1780,139 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="9"/>
+      <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" s="9"/>
+      <c r="C3" s="8"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="C4" s="9"/>
+      <c r="C4" s="8"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="C5" s="9"/>
+      <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="C6" s="9"/>
+      <c r="C6" s="8"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="C7" s="9"/>
+      <c r="C7" s="8"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="C8" s="9"/>
+      <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="C9" s="9"/>
+      <c r="C9" s="8"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="C10" s="9"/>
+      <c r="C10" s="8"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="C11" s="9"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="C12" s="9"/>
+      <c r="C12" s="8"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="C13" s="9"/>
+      <c r="C13" s="8"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="C14" s="9"/>
+      <c r="C14" s="8"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="C15" s="9"/>
+      <c r="C15" s="8"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="C16" s="9"/>
+      <c r="C16" s="8"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="C17" s="9"/>
+      <c r="C17" s="8"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="C18" s="9"/>
+      <c r="C18" s="8"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="C19" s="9"/>
+      <c r="C19" s="8"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="C20" s="9"/>
+      <c r="C20" s="8"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="C21" s="9"/>
+      <c r="C21" s="8"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="C22" s="9"/>
+      <c r="C22" s="8"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="C24" s="9"/>
+      <c r="C24" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -2003,7 +1983,7 @@
       <c r="K1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2163,17 +2143,17 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F2:F31">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Rare"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F32">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Uncommon"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"Common"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F31">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"Rare"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -2235,16 +2215,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="24" x14ac:dyDescent="0.4">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="G2" s="7" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="G2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="7"/>
+      <c r="H2" s="10"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -2268,7 +2248,7 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>

--- a/Assets/Data/Data.xlsx
+++ b/Assets/Data/Data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="50">
   <si>
     <t xml:space="preserve">Num Code</t>
   </si>
@@ -272,9 +272,6 @@
   </si>
   <si>
     <t xml:space="preserve">gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource.png</t>
   </si>
   <si>
     <t xml:space="preserve">pop-growth</t>
@@ -1895,7 +1892,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1903,12 +1900,12 @@
         <v>20</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>47</v>
@@ -1951,12 +1948,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Data.xlsx
+++ b/Assets/Data/Data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="70">
   <si>
     <t xml:space="preserve">Num Code</t>
   </si>
@@ -97,49 +97,13 @@
     <t xml:space="preserve">archer</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">lancer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">-maker</t>
-    </r>
+    <t xml:space="preserve">lancer-maker</t>
   </si>
   <si>
     <t xml:space="preserve">lancer</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">-maker</t>
-    </r>
+    <t xml:space="preserve">cavalry-maker</t>
   </si>
   <si>
     <t xml:space="preserve">cavalry</t>
@@ -151,100 +115,76 @@
     <t xml:space="preserve">giant</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">assassin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">-maker</t>
-    </r>
+    <t xml:space="preserve">assassin-maker</t>
   </si>
   <si>
     <t xml:space="preserve">assassin</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">gunner</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">-maker</t>
-    </r>
+    <t xml:space="preserve">soldier-maker</t>
   </si>
   <si>
     <t xml:space="preserve">gunner</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">peasant</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">-maker</t>
-    </r>
+    <t xml:space="preserve">god-maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">god</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunner-maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peasant-maker</t>
   </si>
   <si>
     <t xml:space="preserve">peasant</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">god</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">-maker</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">god</t>
+    <t xml:space="preserve">mage-tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-nest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">makes dragon eggs. Basic dragon structure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">egg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-hatchery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gem-mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">basic resource structure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-rider-roost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon-rider</t>
   </si>
   <si>
     <t xml:space="preserve">Structure</t>
@@ -268,16 +208,28 @@
     <t xml:space="preserve">Move Speed</t>
   </si>
   <si>
+    <t xml:space="preserve">description of the unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes about the unit</t>
+  </si>
+  <si>
     <t xml:space="preserve">unit</t>
   </si>
   <si>
+    <t xml:space="preserve">soldier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-rider</t>
+  </si>
+  <si>
     <t xml:space="preserve">gold</t>
   </si>
   <si>
+    <t xml:space="preserve">Resource.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">pop-growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uncommon</t>
   </si>
   <si>
     <t xml:space="preserve">Rare</t>
@@ -290,7 +242,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,12 +286,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -547,55 +493,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -762,8 +708,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="UnitData" displayName="UnitData" ref="A1:M10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="UnitData" displayName="UnitData" ref="A1:M12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M12"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Num Code"/>
     <tableColumn id="2" name="Name"/>
@@ -959,465 +905,730 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="H2" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" s="6" t="s">
+      <c r="I2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="9" t="n">
+      <c r="N2" s="10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="6" t="s">
+      <c r="I3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="9" t="n">
+      <c r="N3" s="10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" s="6" t="s">
+      <c r="I4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" s="6" t="s">
+      <c r="I5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="9" t="n">
+      <c r="N5" s="10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="6" t="s">
+      <c r="I6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="9" t="n">
+      <c r="N6" s="10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" s="6" t="s">
+      <c r="I7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N7" s="9" t="n">
+      <c r="N7" s="10" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" s="6" t="s">
+      <c r="I8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="N8" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n">
+      <c r="N8" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="7" t="n">
+      <c r="I11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="N9" s="9" t="n">
+      <c r="K11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="N11" s="10" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="6" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N10" s="9" t="n">
+      <c r="H15" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="N16" s="10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G10" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G16" type="list">
       <formula1>INDIRECT("RarityData")</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1440,416 +1651,524 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L2" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M2" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="G14" s="7"/>
+      <c r="H14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="J2" s="6" t="n">
+      <c r="K14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K2" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" s="6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M2" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M6" s="6" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" s="6" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>2</v>
+      <c r="M14" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G10" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G14" type="list">
       <formula1>INDIRECT("StructureData[Name]")</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1872,11 +2191,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1888,27 +2207,43 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>47</v>
+      <c r="B5" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1933,7 +2268,7 @@
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1942,18 +2277,18 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>48</v>
+      <c r="A3" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>49</v>
+      <c r="A4" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Data.xlsx
+++ b/Assets/Data/Data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="91">
   <si>
     <t xml:space="preserve">Num Code</t>
   </si>
@@ -67,13 +67,7 @@
     <t xml:space="preserve">Output Value</t>
   </si>
   <si>
-    <t xml:space="preserve">knight-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ipsem lorem description bullshit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ipsem lorem notes bullshit</t>
+    <t xml:space="preserve">garrison</t>
   </si>
   <si>
     <t xml:space="preserve">structure</t>
@@ -91,7 +85,7 @@
     <t xml:space="preserve">knight</t>
   </si>
   <si>
-    <t xml:space="preserve">archer-maker</t>
+    <t xml:space="preserve">lechery</t>
   </si>
   <si>
     <t xml:space="preserve">archer</t>
@@ -103,7 +97,7 @@
     <t xml:space="preserve">lancer</t>
   </si>
   <si>
-    <t xml:space="preserve">cavalry-maker</t>
+    <t xml:space="preserve">stable</t>
   </si>
   <si>
     <t xml:space="preserve">cavalry</t>
@@ -115,28 +109,37 @@
     <t xml:space="preserve">giant</t>
   </si>
   <si>
-    <t xml:space="preserve">assassin-maker</t>
+    <t xml:space="preserve">assasins-guild</t>
   </si>
   <si>
     <t xml:space="preserve">assassin</t>
   </si>
   <si>
-    <t xml:space="preserve">soldier-maker</t>
+    <t xml:space="preserve">barracks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soldier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">god-maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">debug tool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">god</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunsmith</t>
   </si>
   <si>
     <t xml:space="preserve">gunner</t>
   </si>
   <si>
-    <t xml:space="preserve">god-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">god</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gunner-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peasant-maker</t>
+    <t xml:space="preserve">Peasant-homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peasantry</t>
   </si>
   <si>
     <t xml:space="preserve">peasant</t>
@@ -148,6 +151,9 @@
     <t xml:space="preserve">Magic</t>
   </si>
   <si>
+    <t xml:space="preserve">gems</t>
+  </si>
+  <si>
     <t xml:space="preserve">mage</t>
   </si>
   <si>
@@ -160,9 +166,6 @@
     <t xml:space="preserve">Dragon</t>
   </si>
   <si>
-    <t xml:space="preserve">gems</t>
-  </si>
-  <si>
     <t xml:space="preserve">egg</t>
   </si>
   <si>
@@ -184,7 +187,76 @@
     <t xml:space="preserve">Uncommon</t>
   </si>
   <si>
-    <t xml:space="preserve">Dragon-rider</t>
+    <t xml:space="preserve">dragon-rider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pop-growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold-mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold-income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">advanced resource structure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">treasury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold income is not currently implemented. We should uh, do that.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunters-lodge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weak but plentiful ranged units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">could give pop growth + hunters as a unique thing, since they hunt + fight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rare resource structure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trading post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-academy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">advanced mage producer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bigger-mage-tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archmage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crystal refinery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mage-university</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rare mage producer</t>
   </si>
   <si>
     <t xml:space="preserve">Structure</t>
@@ -217,22 +289,13 @@
     <t xml:space="preserve">unit</t>
   </si>
   <si>
-    <t xml:space="preserve">soldier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-rider</t>
+    <t xml:space="preserve">hunter</t>
   </si>
   <si>
     <t xml:space="preserve">gold</t>
   </si>
   <si>
     <t xml:space="preserve">Resource.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pop-growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rare</t>
   </si>
 </sst>
 </file>
@@ -905,7 +968,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.51"/>
@@ -913,7 +976,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="14.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.76"/>
@@ -973,38 +1036,34 @@
       <c r="B2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>21</v>
       </c>
       <c r="N2" s="10" t="n">
         <v>4</v>
@@ -1015,40 +1074,36 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="H3" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J3" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N3" s="10" t="n">
         <v>4</v>
@@ -1059,84 +1114,76 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="H4" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J4" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N4" s="10" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N5" s="10" t="n">
         <v>4</v>
@@ -1147,40 +1194,36 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="G6" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N6" s="10" t="n">
         <v>1</v>
@@ -1191,84 +1234,76 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="G7" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>4</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N7" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="G8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="H8" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N8" s="10" t="n">
         <v>4</v>
@@ -1279,84 +1314,80 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="G9" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>100</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N9" s="10" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="G10" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N10" s="10" t="n">
         <v>1</v>
@@ -1369,38 +1400,34 @@
       <c r="B11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>16</v>
-      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
       <c r="E11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="H11" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J11" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N11" s="10" t="n">
         <v>10</v>
@@ -1411,40 +1438,36 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
       <c r="E12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="H12" s="8" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N12" s="10" t="n">
         <v>1</v>
@@ -1455,40 +1478,38 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>45</v>
-      </c>
       <c r="J13" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N13" s="10" t="n">
         <v>1</v>
@@ -1499,40 +1520,36 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>10</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>1</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N14" s="10" t="n">
         <v>1</v>
@@ -1543,92 +1560,550 @@
         <v>15</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D15" s="7"/>
       <c r="E15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D17" s="7"/>
+      <c r="E17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="9" t="s">
+      <c r="H17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N18" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="L16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="7" t="s">
+      <c r="B20" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N16" s="10" t="n">
-        <v>1</v>
+      <c r="H20" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N22" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N26" s="10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="N27" s="10" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G16" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G27" type="list">
       <formula1>INDIRECT("RarityData")</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1651,10 +2126,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.57"/>
@@ -1686,25 +2162,25 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1712,19 +2188,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7" t="n">
@@ -1751,15 +2227,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7" t="n">
@@ -1775,7 +2251,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>1</v>
@@ -1786,15 +2262,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="n">
@@ -1821,15 +2297,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7" t="n">
@@ -1856,15 +2332,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="n">
@@ -1891,15 +2367,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="n">
@@ -1926,15 +2402,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="n">
@@ -1961,15 +2437,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="n">
@@ -1996,15 +2472,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="n">
@@ -2031,25 +2507,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4</v>
@@ -2066,15 +2542,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+        <v>34</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="E12" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7" t="n">
@@ -2096,20 +2576,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7" t="n">
@@ -2131,20 +2611,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7" t="n">
@@ -2157,18 +2637,88 @@
         <v>15</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" s="7" t="n">
         <v>3</v>
       </c>
       <c r="M14" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" s="7" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G14" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G16" type="list">
       <formula1>INDIRECT("StructureData[Name]")</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2191,7 +2741,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
@@ -2208,42 +2758,50 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2278,12 +2836,12 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Assets/Data/Data.xlsx
+++ b/Assets/Data/Data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="84">
   <si>
     <t xml:space="preserve">Num Code</t>
   </si>
@@ -70,6 +70,9 @@
     <t xml:space="preserve">garrison</t>
   </si>
   <si>
+    <t xml:space="preserve">notes</t>
+  </si>
+  <si>
     <t xml:space="preserve">structure</t>
   </si>
   <si>
@@ -85,7 +88,7 @@
     <t xml:space="preserve">knight</t>
   </si>
   <si>
-    <t xml:space="preserve">lechery</t>
+    <t xml:space="preserve">flechery</t>
   </si>
   <si>
     <t xml:space="preserve">archer</t>
@@ -124,178 +127,154 @@
     <t xml:space="preserve">god-maker</t>
   </si>
   <si>
+    <t xml:space="preserve">god</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunsmith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peasant-homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peasantry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peasant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-nest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">egg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-hatchery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gem-mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-rider-roost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-rider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pop-growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold-mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold-income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">treasury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunters-lodge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">this is a long sentence. I am testing if this breaks. We will see</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trading-post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-academy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bigger-mage-tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archmage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crystal-refinery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-university</t>
+  </si>
+  <si>
+    <t xml:space="preserve">work-house</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peasant-lodge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description of the unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes about the unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unit</t>
+  </si>
+  <si>
     <t xml:space="preserve">debug tool</t>
   </si>
   <si>
-    <t xml:space="preserve">god</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gunsmith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gunner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peasant-homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peasantry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peasant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mage-tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-nest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">makes dragon eggs. Basic dragon structure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">egg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-hatchery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gem-mine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">basic resource structure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-rider-roost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uncommon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-rider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">farm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pop-growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold-mine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold-income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">granary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">advanced resource structure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">treasury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold income is not currently implemented. We should uh, do that.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hunters-lodge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weak but plentiful ranged units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">could give pop growth + hunters as a unique thing, since they hunt + fight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hunters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rare resource structure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trading post</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mage-academy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">advanced mage producer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bigger-mage-tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archmage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crystal refinery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mage-university</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rare mage producer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Move Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description of the unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notes about the unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hunter</t>
-  </si>
-  <si>
     <t xml:space="preserve">gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource.png</t>
   </si>
 </sst>
 </file>
@@ -968,11 +947,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.14"/>
@@ -1036,34 +1015,38 @@
       <c r="B2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N2" s="10" t="n">
         <v>4</v>
@@ -1074,36 +1057,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
+        <v>21</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" s="10" t="n">
         <v>4</v>
@@ -1114,36 +1101,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+        <v>23</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N4" s="10" t="n">
         <v>4</v>
@@ -1154,36 +1145,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
+        <v>25</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5" s="10" t="n">
         <v>4</v>
@@ -1194,76 +1189,84 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N6" s="10" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
+        <v>29</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>4</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N7" s="10" t="n">
         <v>2</v>
@@ -1274,36 +1277,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>2</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N8" s="10" t="n">
         <v>4</v>
@@ -1314,34 +1321,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>2</v>
@@ -1360,28 +1367,32 @@
       <c r="B10" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="C10" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>2</v>
@@ -1393,35 +1404,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
+      <c r="C11" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>2</v>
@@ -1430,7 +1445,7 @@
         <v>39</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1440,31 +1455,35 @@
       <c r="B12" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+      <c r="C12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>43</v>
@@ -1481,17 +1500,19 @@
         <v>44</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="G13" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>2</v>
@@ -1503,53 +1524,57 @@
         <v>3</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N13" s="10" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+        <v>47</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>10</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>1</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N14" s="10" t="n">
         <v>1</v>
@@ -1560,32 +1585,34 @@
         <v>15</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>38</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>0</v>
@@ -1594,7 +1621,7 @@
         <v>42</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1602,36 +1629,40 @@
         <v>16</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>54</v>
       </c>
       <c r="N16" s="10" t="n">
         <v>1</v>
@@ -1642,38 +1673,40 @@
         <v>17</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>38</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N17" s="10" t="n">
         <v>1</v>
@@ -1684,38 +1717,40 @@
         <v>18</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>38</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>2</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N18" s="10" t="n">
         <v>1</v>
@@ -1726,26 +1761,28 @@
         <v>19</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>38</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>1</v>
@@ -1757,39 +1794,39 @@
         <v>2</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="n">
         <v>20</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>38</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>4</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="8" t="n">
         <v>1</v>
@@ -1801,10 +1838,10 @@
         <v>2</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N20" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1812,40 +1849,40 @@
         <v>21</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>38</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>5</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="N21" s="10" t="n">
         <v>10</v>
@@ -1856,26 +1893,28 @@
         <v>22</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>38</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>1</v>
@@ -1887,10 +1926,10 @@
         <v>3</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1898,26 +1937,28 @@
         <v>23</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>38</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>1</v>
@@ -1929,10 +1970,10 @@
         <v>3</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1940,20 +1981,22 @@
         <v>24</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>6</v>
@@ -1965,7 +2008,7 @@
         <v>3</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L24" s="8" t="n">
         <v>3</v>
@@ -1982,18 +2025,22 @@
         <v>25</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
+        <v>66</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>6</v>
@@ -2005,13 +2052,13 @@
         <v>1</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L25" s="8" t="n">
         <v>1</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N25" s="10" t="n">
         <v>1</v>
@@ -2022,62 +2069,66 @@
         <v>26</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="7" t="s">
         <v>42</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="n">
         <v>27</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>10</v>
@@ -2089,21 +2140,109 @@
         <v>3</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L27" s="8" t="n">
         <v>3</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N27" s="10" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N28" s="10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G27" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G29" type="list">
       <formula1>INDIRECT("RarityData")</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2162,25 +2301,25 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="M1" s="12" t="s">
         <v>78</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2188,19 +2327,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7" t="n">
@@ -2227,15 +2366,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
+        <v>22</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="E3" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7" t="n">
@@ -2262,15 +2405,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+        <v>24</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="E4" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="n">
@@ -2297,15 +2444,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
+        <v>26</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="E5" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7" t="n">
@@ -2332,25 +2483,29 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+        <v>28</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="E6" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>0.5</v>
@@ -2367,15 +2522,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
+        <v>30</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="E7" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="n">
@@ -2402,15 +2561,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+        <v>32</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="E8" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="n">
@@ -2437,15 +2600,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
+        <v>48</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="E9" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="n">
@@ -2474,13 +2641,17 @@
       <c r="B10" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="C10" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="E10" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="n">
@@ -2509,10 +2680,14 @@
       <c r="B11" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
+      <c r="C11" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="E11" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>38</v>
@@ -2545,16 +2720,16 @@
         <v>34</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7" t="n">
@@ -2581,15 +2756,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
+        <v>52</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="E13" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7" t="n">
@@ -2618,10 +2797,14 @@
       <c r="B14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+      <c r="C14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="E14" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>41</v>
@@ -2637,7 +2820,7 @@
         <v>15</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" s="7" t="n">
         <v>3</v>
@@ -2651,12 +2834,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
+        <v>61</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="E15" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>38</v>
@@ -2683,15 +2870,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+        <v>67</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="E16" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>41</v>
@@ -2707,7 +2898,7 @@
         <v>30</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L16" s="7" t="n">
         <v>4</v>
@@ -2758,34 +2949,34 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2793,15 +2984,15 @@
         <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2836,17 +3027,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Data.xlsx
+++ b/Assets/Data/Data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="1" state="visible" r:id="rId3"/>
@@ -175,6 +175,9 @@
     <t xml:space="preserve">gem-mine</t>
   </si>
   <si>
+    <t xml:space="preserve">gem-income</t>
+  </si>
+  <si>
     <t xml:space="preserve">dragon-rider-roost</t>
   </si>
   <si>
@@ -193,33 +196,33 @@
     <t xml:space="preserve">gold-mine</t>
   </si>
   <si>
-    <t xml:space="preserve">gold-income</t>
+    <t xml:space="preserve">gold</t>
   </si>
   <si>
     <t xml:space="preserve">granary</t>
   </si>
   <si>
+    <t xml:space="preserve">trading-post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunters-lodge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">this is a long sentence. I am testing if this breaks. We will see</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rare</t>
+  </si>
+  <si>
     <t xml:space="preserve">treasury</t>
   </si>
   <si>
-    <t xml:space="preserve">hunters-lodge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">this is a long sentence. I am testing if this breaks. We will see</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hunter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trading-post</t>
-  </si>
-  <si>
     <t xml:space="preserve">mage-academy</t>
   </si>
   <si>
@@ -272,9 +275,6 @@
   </si>
   <si>
     <t xml:space="preserve">debug tool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold</t>
   </si>
 </sst>
 </file>
@@ -1521,7 +1521,7 @@
         <v>42</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>19</v>
@@ -1618,10 +1618,10 @@
         <v>0</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1629,7 +1629,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>2</v>
@@ -1644,7 +1644,7 @@
         <v>45</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H16" s="8" t="n">
         <v>15</v>
@@ -1662,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N16" s="10" t="n">
         <v>1</v>
@@ -1673,7 +1673,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>2</v>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" s="10" t="n">
         <v>1</v>
@@ -1717,7 +1717,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>2</v>
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N18" s="10" t="n">
         <v>1</v>
@@ -1761,7 +1761,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>2</v>
@@ -1776,7 +1776,7 @@
         <v>38</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>3</v>
@@ -1794,7 +1794,7 @@
         <v>2</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N19" s="10" t="n">
         <v>2</v>
@@ -1805,7 +1805,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>2</v>
@@ -1820,7 +1820,7 @@
         <v>38</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>4</v>
@@ -1838,7 +1838,7 @@
         <v>2</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N20" s="10" t="n">
         <v>2</v>
@@ -1849,13 +1849,13 @@
         <v>21</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>16</v>
@@ -1882,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N21" s="10" t="n">
         <v>10</v>
@@ -1893,7 +1893,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>2</v>
@@ -1908,7 +1908,7 @@
         <v>38</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>7</v>
@@ -1926,7 +1926,7 @@
         <v>3</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N22" s="10" t="n">
         <v>3</v>
@@ -1937,7 +1937,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>2</v>
@@ -1952,7 +1952,7 @@
         <v>38</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>8</v>
@@ -1970,7 +1970,7 @@
         <v>3</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N23" s="10" t="n">
         <v>3</v>
@@ -1981,7 +1981,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>2</v>
@@ -1996,7 +1996,7 @@
         <v>41</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>6</v>
@@ -2025,7 +2025,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>2</v>
@@ -2040,16 +2040,16 @@
         <v>41</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>42</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>19</v>
@@ -2058,7 +2058,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N25" s="10" t="n">
         <v>1</v>
@@ -2069,7 +2069,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>2</v>
@@ -2084,7 +2084,7 @@
         <v>41</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
         <v>0</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2113,7 +2113,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>2</v>
@@ -2128,7 +2128,7 @@
         <v>41</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
         <v>3</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N27" s="10" t="n">
         <v>3</v>
@@ -2157,7 +2157,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>2</v>
@@ -2172,7 +2172,7 @@
         <v>38</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>3</v>
@@ -2201,7 +2201,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>2</v>
@@ -2216,7 +2216,7 @@
         <v>38</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>6</v>
@@ -2301,25 +2301,25 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2330,13 +2330,13 @@
         <v>20</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>17</v>
@@ -2369,13 +2369,13 @@
         <v>22</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>17</v>
@@ -2408,13 +2408,13 @@
         <v>24</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>17</v>
@@ -2447,13 +2447,13 @@
         <v>26</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>17</v>
@@ -2486,13 +2486,13 @@
         <v>28</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>17</v>
@@ -2525,13 +2525,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>17</v>
@@ -2564,13 +2564,13 @@
         <v>32</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>17</v>
@@ -2603,13 +2603,13 @@
         <v>48</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>45</v>
@@ -2642,13 +2642,13 @@
         <v>36</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>17</v>
@@ -2681,13 +2681,13 @@
         <v>39</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>38</v>
@@ -2720,13 +2720,13 @@
         <v>34</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>81</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>17</v>
@@ -2756,16 +2756,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>45</v>
@@ -2798,13 +2798,13 @@
         <v>43</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>41</v>
@@ -2834,16 +2834,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>38</v>
@@ -2873,16 +2873,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>41</v>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2965,10 +2965,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2989,10 +2989,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3032,12 +3032,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Data.xlsx
+++ b/Assets/Data/Data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="82">
   <si>
     <t xml:space="preserve">Num Code</t>
   </si>
@@ -136,72 +136,75 @@
     <t xml:space="preserve">gunner</t>
   </si>
   <si>
-    <t xml:space="preserve">peasant-homes</t>
+    <t xml:space="preserve">gem-transmutator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gem-income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-nest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">egg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-hatchery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gem-mine</t>
   </si>
   <si>
     <t xml:space="preserve">Peasantry</t>
   </si>
   <si>
+    <t xml:space="preserve">dragon-rider-roost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-rider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pop-growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold-mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granary</t>
+  </si>
+  <si>
     <t xml:space="preserve">peasant</t>
   </si>
   <si>
-    <t xml:space="preserve">mage-tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-nest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">egg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-hatchery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gem-mine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gem-income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-rider-roost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uncommon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-rider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">farm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pop-growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold-mine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">granary</t>
-  </si>
-  <si>
     <t xml:space="preserve">trading-post</t>
   </si>
   <si>
@@ -217,9 +220,6 @@
     <t xml:space="preserve">mill</t>
   </si>
   <si>
-    <t xml:space="preserve">Rare</t>
-  </si>
-  <si>
     <t xml:space="preserve">treasury</t>
   </si>
   <si>
@@ -236,12 +236,6 @@
   </si>
   <si>
     <t xml:space="preserve">mage-university</t>
-  </si>
-  <si>
-    <t xml:space="preserve">work-house</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peasant-lodge</t>
   </si>
   <si>
     <t xml:space="preserve">Structure</t>
@@ -947,7 +941,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.51"/>
@@ -1037,7 +1031,7 @@
         <v>19</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>19</v>
@@ -1081,7 +1075,7 @@
         <v>19</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>19</v>
@@ -1125,7 +1119,7 @@
         <v>19</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>19</v>
@@ -1169,7 +1163,7 @@
         <v>19</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>19</v>
@@ -1257,7 +1251,7 @@
         <v>19</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>19</v>
@@ -1301,7 +1295,7 @@
         <v>19</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>19</v>
@@ -1424,16 +1418,16 @@
         <v>38</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>19</v>
@@ -1442,7 +1436,7 @@
         <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N11" s="10" t="n">
         <v>5</v>
@@ -1453,7 +1447,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>2</v>
@@ -1465,7 +1459,7 @@
         <v>16</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>18</v>
@@ -1474,7 +1468,7 @@
         <v>5</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>2</v>
@@ -1486,7 +1480,7 @@
         <v>1</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N12" s="10" t="n">
         <v>1</v>
@@ -1497,7 +1491,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>2</v>
@@ -1509,7 +1503,7 @@
         <v>16</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>18</v>
@@ -1518,7 +1512,7 @@
         <v>2</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>2</v>
@@ -1530,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N13" s="10" t="n">
         <v>1</v>
@@ -1541,7 +1535,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>2</v>
@@ -1553,16 +1547,16 @@
         <v>16</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>18</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>1</v>
@@ -1574,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N14" s="10" t="n">
         <v>1</v>
@@ -1585,7 +1579,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>2</v>
@@ -1597,7 +1591,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>18</v>
@@ -1618,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="N15" s="10" t="n">
         <v>1</v>
@@ -1629,7 +1623,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>2</v>
@@ -1641,16 +1635,16 @@
         <v>16</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J16" s="8" t="n">
         <v>1</v>
@@ -1662,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N16" s="10" t="n">
         <v>1</v>
@@ -1673,7 +1667,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>2</v>
@@ -1685,7 +1679,7 @@
         <v>16</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>18</v>
@@ -1706,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N17" s="10" t="n">
         <v>1</v>
@@ -1717,7 +1711,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>2</v>
@@ -1729,7 +1723,7 @@
         <v>16</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>18</v>
@@ -1750,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="N18" s="10" t="n">
         <v>1</v>
@@ -1773,10 +1767,10 @@
         <v>16</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>3</v>
@@ -1788,13 +1782,13 @@
         <v>1</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N19" s="10" t="n">
         <v>2</v>
@@ -1805,7 +1799,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>2</v>
@@ -1817,10 +1811,10 @@
         <v>16</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>4</v>
@@ -1829,16 +1823,16 @@
         <v>19</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="N20" s="10" t="n">
         <v>2</v>
@@ -1849,19 +1843,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>18</v>
@@ -1873,7 +1867,7 @@
         <v>19</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>19</v>
@@ -1882,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N21" s="10" t="n">
         <v>10</v>
@@ -1893,7 +1887,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>2</v>
@@ -1905,10 +1899,10 @@
         <v>16</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>7</v>
@@ -1920,13 +1914,13 @@
         <v>1</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>3</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N22" s="10" t="n">
         <v>3</v>
@@ -1949,10 +1943,10 @@
         <v>16</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>8</v>
@@ -1964,13 +1958,13 @@
         <v>1</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L23" s="8" t="n">
         <v>3</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="N23" s="10" t="n">
         <v>3</v>
@@ -1993,16 +1987,16 @@
         <v>16</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J24" s="8" t="n">
         <v>3</v>
@@ -2014,7 +2008,7 @@
         <v>3</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N24" s="10" t="n">
         <v>3</v>
@@ -2037,16 +2031,16 @@
         <v>16</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>8</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>2</v>
@@ -2081,10 +2075,10 @@
         <v>16</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>10</v>
@@ -2102,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="N26" s="10" t="n">
         <v>3</v>
@@ -2125,16 +2119,16 @@
         <v>16</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>10</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J27" s="8" t="n">
         <v>3</v>
@@ -2152,97 +2146,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J28" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N28" s="10" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M29" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N29" s="10" t="n">
-        <v>30</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G29" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G27" type="list">
       <formula1>INDIRECT("RarityData")</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2301,25 +2207,25 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="12" t="s">
         <v>77</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2330,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>17</v>
@@ -2369,13 +2275,13 @@
         <v>22</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>17</v>
@@ -2408,13 +2314,13 @@
         <v>24</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>17</v>
@@ -2447,13 +2353,13 @@
         <v>26</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>17</v>
@@ -2486,13 +2392,13 @@
         <v>28</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>17</v>
@@ -2525,13 +2431,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>17</v>
@@ -2564,13 +2470,13 @@
         <v>32</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>17</v>
@@ -2600,29 +2506,29 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>10</v>
@@ -2642,13 +2548,13 @@
         <v>36</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>17</v>
@@ -2678,19 +2584,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="F11" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="n">
@@ -2720,13 +2626,13 @@
         <v>34</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>17</v>
@@ -2756,29 +2662,29 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="F13" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>10</v>
@@ -2795,19 +2701,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="F14" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7" t="n">
@@ -2834,19 +2740,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="F15" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7" t="n">
@@ -2876,16 +2782,16 @@
         <v>68</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="F16" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="n">
@@ -2949,10 +2855,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2965,34 +2871,34 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -3032,12 +2938,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Data.xlsx
+++ b/Assets/Data/Data.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="107">
   <si>
     <t xml:space="preserve">Num Code</t>
   </si>
@@ -49,22 +49,7 @@
     <t xml:space="preserve">Gold Cost</t>
   </si>
   <si>
-    <t xml:space="preserve">Resource 1 In</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input 1 Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource 2 In</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input 2 Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource Out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Output Value</t>
+    <t xml:space="preserve">Transaction</t>
   </si>
   <si>
     <t xml:space="preserve">garrison</t>
@@ -82,193 +67,367 @@
     <t xml:space="preserve">Common</t>
   </si>
   <si>
+    <t xml:space="preserve">input=population:4;
+output=knight:4;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flechery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:4;
+output=archer:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lancer-maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:4;
+output=lancer:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:4;
+output=cavalry:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">giant-maker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=giant:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assasins-guild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:2;
+output=assassin:2|gems:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barracks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:4;
+output=soldier:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1|gems:1;
+output=druid:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunsmith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=gunner:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gem-transmutator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=gold:1;
+output=gems:5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=gems:2;
+output=mage:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-nest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=gems:2;
+output=egg:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-hatchery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=egg:1;
+output=dragon:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gem-mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peasantry</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">input=population:1;
+output=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">gem-income</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-rider-roost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=dragon:1;
+output=dragon-rider:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=pop-growth:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold-mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=gold:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=pop-growth:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trading-post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=gold:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunters-lodge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">this is a long sentence. I am testing if this breaks. We will see</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:5;
+output=hunter:5|pop-growth:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=pop-growth:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">treasury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:3;
+output=gold:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-academy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1|gems:1;
+output=mage:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bigger-mage-tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:3|gems:1;
+output=mage:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crystal-refinery</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">input=population:2;
+output=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">gem-income</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">mage-university</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=gems:3;
+output=archmage:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description of the unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes about the unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile-speed=3;
+projectile-sprite=arrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cavalry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">giant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soldier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunner</t>
+  </si>
+  <si>
     <t xml:space="preserve">population</t>
   </si>
   <si>
-    <t xml:space="preserve">knight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flechery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lancer-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cavalry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">giant-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">giant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assasins-guild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assassin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">barracks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soldier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">god-maker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">god</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gunsmith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gunner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gem-transmutator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rare</t>
+    <t xml:space="preserve">druid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile-speed=3;
+projectile-sprite=magic-blast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-rider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archmage</t>
   </si>
   <si>
     <t xml:space="preserve">gold</t>
   </si>
   <si>
+    <t xml:space="preserve">pop-growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">egg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gems</t>
+  </si>
+  <si>
     <t xml:space="preserve">gem-income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mage-tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-nest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">egg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-hatchery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gem-mine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peasantry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-rider-roost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uncommon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-rider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">farm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pop-growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold-mine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">granary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peasant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trading-post</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hunters-lodge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">this is a long sentence. I am testing if this breaks. We will see</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hunter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">treasury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mage-academy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bigger-mage-tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archmage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crystal-refinery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mage-university</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Move Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description of the unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notes about the unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">debug tool</t>
   </si>
 </sst>
 </file>
@@ -278,7 +437,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,6 +480,19 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -499,7 +671,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -523,8 +695,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -561,6 +736,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -577,18 +756,35 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="data" xfId="20"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -733,33 +929,32 @@
     <tableColumn id="6" name="Archetype"/>
     <tableColumn id="7" name="Rarity"/>
     <tableColumn id="8" name="Gold Cost"/>
-    <tableColumn id="9" name="Resource 1 In"/>
-    <tableColumn id="10" name="Input 1 Value"/>
-    <tableColumn id="11" name="Resource 2 In"/>
-    <tableColumn id="12" name="Input 2 Value"/>
-    <tableColumn id="13" name="Resource Out"/>
-    <tableColumn id="14" name="Output Value"/>
+    <tableColumn id="9" name="Transaction"/>
+    <tableColumn id="10" name=""/>
+    <tableColumn id="11" name=""/>
+    <tableColumn id="12" name=""/>
+    <tableColumn id="13" name=""/>
+    <tableColumn id="14" name=""/>
   </tableColumns>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="UnitData" displayName="UnitData" ref="A1:M12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M12"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="UnitData" displayName="UnitData" ref="A1:L12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L12"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="Num Code"/>
     <tableColumn id="2" name="Name"/>
     <tableColumn id="3" name="Description"/>
     <tableColumn id="4" name="Notes"/>
     <tableColumn id="5" name="Sprite"/>
     <tableColumn id="6" name="Archetype"/>
-    <tableColumn id="7" name="Structure"/>
-    <tableColumn id="8" name="Size"/>
-    <tableColumn id="9" name="Health"/>
-    <tableColumn id="10" name="Attack"/>
-    <tableColumn id="11" name="Attack Speed"/>
-    <tableColumn id="12" name="Attack Range"/>
-    <tableColumn id="13" name="Move Speed"/>
+    <tableColumn id="7" name="Size"/>
+    <tableColumn id="8" name="Health"/>
+    <tableColumn id="9" name="Attack"/>
+    <tableColumn id="10" name="Attack Speed"/>
+    <tableColumn id="11" name="Attack Range"/>
+    <tableColumn id="12" name="Move Speed"/>
   </tableColumns>
 </table>
 </file>
@@ -941,7 +1136,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.51"/>
@@ -951,7 +1146,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.29"/>
@@ -986,1124 +1182,864 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="5"/>
+    </row>
+    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H2" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="10" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="J2" s="8"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="11"/>
+    </row>
+    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" s="10" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>16</v>
+      </c>
+      <c r="J3" s="8"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="11"/>
+    </row>
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="10" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="C5" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="10" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+      <c r="J5" s="8"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>4</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N7" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>2</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="J8" s="8"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="K8" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="10" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>1000</v>
-      </c>
       <c r="I9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N9" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>29</v>
+      </c>
+      <c r="J9" s="8"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="N10" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N11" s="10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>35</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="N12" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="J12" s="8"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>2</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>40</v>
+      </c>
+      <c r="J13" s="8"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="N14" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="J14" s="8"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="n">
         <v>15</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N15" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>45</v>
+      </c>
+      <c r="J15" s="8"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>16</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H16" s="8" t="n">
         <v>10</v>
       </c>
       <c r="I16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="8"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="11"/>
+    </row>
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="N16" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="C17" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>2</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="N17" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>50</v>
+      </c>
+      <c r="J17" s="8"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="n">
         <v>18</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>2</v>
       </c>
       <c r="I18" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="8"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="N18" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="n">
-        <v>19</v>
-      </c>
       <c r="B19" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="L19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="N19" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="n">
         <v>20</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>4</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="N20" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="J20" s="8"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="n">
         <v>21</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="N21" s="10" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>59</v>
+      </c>
+      <c r="J21" s="8"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="n">
         <v>22</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>7</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="N22" s="10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="J22" s="8"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12" t="n">
         <v>23</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>8</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="L23" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="N23" s="10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+      <c r="J23" s="8"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="n">
         <v>24</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="N24" s="10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="J24" s="8"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="11"/>
+    </row>
+    <row r="25" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="n">
         <v>25</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>8</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="N25" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>67</v>
+      </c>
+      <c r="J25" s="8"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="11"/>
+    </row>
+    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="n">
         <v>26</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J26" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N26" s="10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="n">
+      <c r="J26" s="8"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="n">
         <v>27</v>
       </c>
       <c r="B27" s="7" t="s">
@@ -2113,42 +2049,42 @@
         <v>2</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>10</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J27" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="N27" s="10" t="n">
-        <v>3</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="J27" s="8"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I29" s="9"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G27" type="list">
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G8 G10:G27" type="list">
+      <formula1>INDIRECT("RarityData")</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G9" type="list">
       <formula1>INDIRECT("RarityData")</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2171,7 +2107,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.82"/>
@@ -2180,11 +2116,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="12.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="12.8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2207,25 +2144,28 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="L1" s="13" t="s">
         <v>77</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2233,77 +2173,85 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="7"/>
+        <v>12</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="H2" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N2" s="14"/>
+    </row>
+    <row r="3" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="J2" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K2" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L2" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M2" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="7"/>
       <c r="H3" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="K3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="7" t="n">
-        <v>1</v>
+      <c r="M3" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2311,515 +2259,558 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="7"/>
+        <v>12</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="H4" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" s="7" t="n">
+      <c r="K4" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N4" s="14"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K4" s="7" t="n">
+      <c r="B5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M4" s="7" t="n">
+      <c r="H5" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="7" t="n">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="J5" s="7" t="n">
+      <c r="L5" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="M5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="7"/>
+        <v>12</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="H6" s="7" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M6" s="7" t="n">
         <v>0.2</v>
       </c>
+      <c r="M6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="7"/>
+        <v>12</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="H7" s="7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>10</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M7" s="7" t="n">
         <v>6</v>
       </c>
+      <c r="M7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="7"/>
+        <v>12</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="H8" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N8" s="14"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>10</v>
-      </c>
       <c r="L9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="7" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M9" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N9" s="15"/>
+    </row>
+    <row r="10" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="7"/>
+        <v>12</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="H10" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="7" t="n">
-        <v>16</v>
-      </c>
       <c r="J10" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="K10" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="7" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="7"/>
       <c r="H11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M11" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M11" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N11" s="15"/>
+    </row>
+    <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>81</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="N12" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
+      <c r="D13" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>180</v>
+      </c>
+      <c r="I13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>180</v>
-      </c>
       <c r="J13" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" s="7" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M13" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N13" s="15"/>
+    </row>
+    <row r="14" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="N14" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" s="7" t="n">
+      <c r="H15" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="K15" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L15" s="7" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M15" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="7"/>
+        <v>33</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="H16" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" s="7" t="n">
-        <v>1</v>
+      <c r="M16" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G16" type="list">
-      <formula1>INDIRECT("StructureData[Name]")</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2846,59 +2837,59 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="18" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2927,23 +2918,23 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Data.xlsx
+++ b/Assets/Data/Data.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="106">
   <si>
     <t xml:space="preserve">Num Code</t>
   </si>
@@ -68,10 +68,10 @@
   </si>
   <si>
     <t xml:space="preserve">input=population:4;
-output=knight:4;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flechery</t>
+output=knight:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fletchery</t>
   </si>
   <si>
     <t xml:space="preserve">input=population:4;
@@ -130,7 +130,7 @@
 output=gunner:1</t>
   </si>
   <si>
-    <t xml:space="preserve">gem-transmutator</t>
+    <t xml:space="preserve">gem-transmutor</t>
   </si>
   <si>
     <t xml:space="preserve">Magic</t>
@@ -171,6 +171,51 @@
   </si>
   <si>
     <t xml:space="preserve">Peasantry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=gem-income:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon-rider-roost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=dragon:1;
+output=dragon-rider:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=pop-growth:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold-mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=gold:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=pop-growth:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trading-post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=population:1;
+output=gold:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunters-lodge</t>
   </si>
   <si>
     <r>
@@ -181,8 +226,8 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">input=population:1;
-output=</t>
+      <t xml:space="preserve">input=population:5;
+output=hunter</t>
     </r>
     <r>
       <rPr>
@@ -191,66 +236,8 @@
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">gem-income</t>
+      <t xml:space="preserve">:5|pop-growth:1</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:1</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon-rider-roost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uncommon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">input=dragon:1;
-output=dragon-rider:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">farm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">input=population:1;
-output=pop-growth:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold-mine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">input=population:1;
-output=gold:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">granary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">input=population:1;
-output=pop-growth:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trading-post</t>
-  </si>
-  <si>
-    <t xml:space="preserve">input=population:1;
-output=gold:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hunters-lodge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">this is a long sentence. I am testing if this breaks. We will see</t>
-  </si>
-  <si>
-    <t xml:space="preserve">input=population:5;
-output=hunter:5|pop-growth:1</t>
   </si>
   <si>
     <t xml:space="preserve">mill</t>
@@ -284,36 +271,8 @@
     <t xml:space="preserve">crystal-refinery</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">input=population:2;
-output=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">gem-income</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:3</t>
-    </r>
+    <t xml:space="preserve">input=population:2;
+output=gem-income:3</t>
   </si>
   <si>
     <t xml:space="preserve">mage-university</t>
@@ -1845,7 +1804,7 @@
         <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>11</v>
@@ -1860,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J21" s="8"/>
       <c r="K21" s="10"/>
@@ -1873,7 +1832,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>2</v>
@@ -1894,7 +1853,7 @@
         <v>7</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="10"/>
@@ -1907,7 +1866,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>2</v>
@@ -1928,7 +1887,7 @@
         <v>8</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J23" s="8"/>
       <c r="K23" s="10"/>
@@ -1941,7 +1900,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>2</v>
@@ -1962,7 +1921,7 @@
         <v>6</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J24" s="8"/>
       <c r="K24" s="10"/>
@@ -1975,7 +1934,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>2</v>
@@ -1996,7 +1955,7 @@
         <v>8</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J25" s="8"/>
       <c r="K25" s="10"/>
@@ -2009,7 +1968,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>2</v>
@@ -2030,7 +1989,7 @@
         <v>10</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J26" s="8"/>
       <c r="K26" s="10"/>
@@ -2043,7 +2002,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>2</v>
@@ -2064,7 +2023,7 @@
         <v>10</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="10"/>
@@ -2120,8 +2079,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="12.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="12.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="12.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="12.8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2144,28 +2103,28 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="M1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,16 +2132,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>12</v>
@@ -2206,25 +2165,25 @@
         <v>2</v>
       </c>
       <c r="M2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="N2" s="14"/>
+    </row>
+    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="N2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>85</v>
-      </c>
       <c r="C3" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>12</v>
@@ -2248,10 +2207,10 @@
         <v>1</v>
       </c>
       <c r="M3" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="N3" s="15" t="s">
         <v>86</v>
-      </c>
-      <c r="N3" s="15" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2259,16 +2218,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>12</v>
@@ -2292,7 +2251,7 @@
         <v>1.5</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N4" s="14"/>
     </row>
@@ -2301,16 +2260,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>12</v>
@@ -2334,7 +2293,7 @@
         <v>3</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N5" s="15"/>
     </row>
@@ -2343,16 +2302,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>12</v>
@@ -2376,7 +2335,7 @@
         <v>0.2</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N6" s="14"/>
     </row>
@@ -2385,16 +2344,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>12</v>
@@ -2418,7 +2377,7 @@
         <v>6</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N7" s="15"/>
     </row>
@@ -2427,16 +2386,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>12</v>
@@ -2460,7 +2419,7 @@
         <v>1.5</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N8" s="14"/>
     </row>
@@ -2469,16 +2428,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>39</v>
@@ -2502,25 +2461,25 @@
         <v>4</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N9" s="15"/>
     </row>
-    <row r="10" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>12</v>
@@ -2544,10 +2503,10 @@
         <v>0.5</v>
       </c>
       <c r="M10" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="N10" s="14" t="s">
         <v>86</v>
-      </c>
-      <c r="N10" s="14" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2555,16 +2514,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>44</v>
@@ -2588,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N11" s="15"/>
     </row>
@@ -2597,16 +2556,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="E12" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>28</v>
@@ -2630,10 +2589,10 @@
         <v>1</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2641,16 +2600,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>39</v>
@@ -2674,25 +2633,25 @@
         <v>4</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N13" s="15"/>
     </row>
-    <row r="14" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>33</v>
@@ -2716,27 +2675,27 @@
         <v>1</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N14" s="14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>44</v>
@@ -2760,27 +2719,27 @@
         <v>1</v>
       </c>
       <c r="M15" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="N15" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="N15" s="15" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>33</v>
@@ -2804,10 +2763,10 @@
         <v>1</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N16" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2846,50 +2805,50 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Data.xlsx
+++ b/Assets/Data/Data.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="114">
   <si>
     <t xml:space="preserve">Num Code</t>
   </si>
@@ -78,7 +78,7 @@
 output=archer:4</t>
   </si>
   <si>
-    <t xml:space="preserve">lancer-maker</t>
+    <t xml:space="preserve">Jousting-arena</t>
   </si>
   <si>
     <t xml:space="preserve">input=population:4;
@@ -140,7 +140,7 @@
   </si>
   <si>
     <t xml:space="preserve">input=gold:1;
-output=gems:5</t>
+output=gem-income:2</t>
   </si>
   <si>
     <t xml:space="preserve">mage-tower</t>
@@ -282,6 +282,23 @@
 output=archmage:3</t>
   </si>
   <si>
+    <t xml:space="preserve">bear-cave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=pop-growth:1;
+output=bear:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophers-tomb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input=pop-growth:1;
+output=gold:2| gem-income:2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Size</t>
   </si>
   <si>
@@ -313,9 +330,6 @@
   </si>
   <si>
     <t xml:space="preserve">notes about the unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unit</t>
   </si>
   <si>
     <t xml:space="preserve">Melee</t>
@@ -355,6 +369,9 @@
     <t xml:space="preserve">population</t>
   </si>
   <si>
+    <t xml:space="preserve">peasant</t>
+  </si>
+  <si>
     <t xml:space="preserve">druid</t>
   </si>
   <si>
@@ -372,6 +389,15 @@
   </si>
   <si>
     <t xml:space="preserve">archmage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fast frontliner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unit</t>
   </si>
   <si>
     <t xml:space="preserve">gold</t>
@@ -1986,7 +2012,7 @@
         <v>47</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>68</v>
@@ -2031,15 +2057,67 @@
       <c r="M27" s="7"/>
       <c r="N27" s="11"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I29" s="9"/>
+    <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G8 G10:G27" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G8 G10:G29" type="list">
       <formula1>INDIRECT("RarityData")</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2066,7 +2144,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.82"/>
@@ -2103,28 +2181,28 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2132,16 +2210,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>12</v>
@@ -2165,7 +2243,7 @@
         <v>2</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N2" s="14"/>
     </row>
@@ -2174,16 +2252,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>12</v>
@@ -2207,10 +2285,10 @@
         <v>1</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2218,16 +2296,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>12</v>
@@ -2251,7 +2329,7 @@
         <v>1.5</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N4" s="14"/>
     </row>
@@ -2260,16 +2338,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>12</v>
@@ -2293,7 +2371,7 @@
         <v>3</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N5" s="15"/>
     </row>
@@ -2302,19 +2380,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>2</v>
@@ -2335,7 +2413,7 @@
         <v>0.2</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N6" s="14"/>
     </row>
@@ -2344,16 +2422,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>12</v>
@@ -2377,7 +2455,7 @@
         <v>6</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N7" s="15"/>
     </row>
@@ -2386,16 +2464,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>12</v>
@@ -2419,7 +2497,7 @@
         <v>1.5</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N8" s="14"/>
     </row>
@@ -2428,16 +2506,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>39</v>
@@ -2461,7 +2539,7 @@
         <v>4</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N9" s="15"/>
     </row>
@@ -2470,16 +2548,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>12</v>
@@ -2503,10 +2581,10 @@
         <v>0.5</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N10" s="14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2514,16 +2592,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>44</v>
@@ -2547,7 +2625,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N11" s="15"/>
     </row>
@@ -2556,16 +2634,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>28</v>
@@ -2589,10 +2667,10 @@
         <v>1</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2600,16 +2678,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>39</v>
@@ -2633,7 +2711,7 @@
         <v>4</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N13" s="15"/>
     </row>
@@ -2642,16 +2720,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>33</v>
@@ -2675,10 +2753,10 @@
         <v>1</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N14" s="14" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2686,16 +2764,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>44</v>
@@ -2719,10 +2797,10 @@
         <v>1</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N15" s="15" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2730,16 +2808,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>33</v>
@@ -2763,11 +2841,53 @@
         <v>1</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N16" s="14" t="s">
-        <v>96</v>
-      </c>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="N17" s="15"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2805,50 +2925,50 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
